--- a/tame_output/ON/bt/strategyON_20240504.xlsx
+++ b/tame_output/ON/bt/strategyON_20240504.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-608.1%</t>
+          <t>-608.0%</t>
         </is>
       </c>
     </row>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.739538806066296</v>
+        <v>3.739538806066297</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.465138622902705</v>
+        <v>-4.464685768985774</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9574391473073585</v>
+        <v>0.957620288874131</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5064601808626168</v>

--- a/tame_output/ON/bt/strategyON_20240504.xlsx
+++ b/tame_output/ON/bt/strategyON_20240504.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.5%</t>
+          <t>115.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-54.9%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-608.0%</t>
+          <t>-598.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-276.6%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353075</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544784</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46470,10 +46470,10 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.464685768985774</v>
+        <v>-4.369279169221332</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.957620288874131</v>
+        <v>0.9957829287799078</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5064601808626168</v>

--- a/tame_output/ON/bt/strategyON_20240504.xlsx
+++ b/tame_output/ON/bt/strategyON_20240504.xlsx
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978373</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>

--- a/tame_output/ON/bt/strategyON_20240504.xlsx
+++ b/tame_output/ON/bt/strategyON_20240504.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-27.7%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>135.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-202.0%</t>
+          <t>-162.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1953"/>
+  <dimension ref="A1:G1954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353075</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544784</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.739538806066297</v>
+        <v>3.733008865660773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
@@ -46480,6 +46480,29 @@
       </c>
       <c r="G1953" t="n">
         <v>2.439974912264618</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="2" t="n">
+        <v>45416</v>
+      </c>
+      <c r="B1954" t="n">
+        <v>3.739226103081856</v>
+      </c>
+      <c r="C1954" t="n">
+        <v>2.838795600967019</v>
+      </c>
+      <c r="D1954" t="n">
+        <v>-4.369279169221332</v>
+      </c>
+      <c r="E1954" t="n">
+        <v>0.9957829287799078</v>
+      </c>
+      <c r="F1954" t="n">
+        <v>-0.5064601808626168</v>
+      </c>
+      <c r="G1954" t="n">
+        <v>2.831859397953386</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240504.xlsx
+++ b/tame_output/ON/bt/strategyON_20240504.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-31.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.4%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.4%</t>
+          <t>134.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-693.6%</t>
+          <t>-685.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-54.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.8%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-598.5%</t>
+          <t>-615.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-274.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-95.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.6%</t>
+          <t>-283.5%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.2%</t>
+          <t>-153.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-162.8%</t>
+          <t>-166.4%</t>
         </is>
       </c>
     </row>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.653473476195825</v>
+        <v>-4.574254890800635</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.275992831771302</v>
+        <v>1.307680265929378</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.8080070932056955</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.085279269345612</v>
+        <v>-5.006060683950422</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.089603401978791</v>
+        <v>1.121290836136868</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.9444245896469625</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.319973263478165</v>
+        <v>-5.240754678082975</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9840105793278613</v>
+        <v>1.015698013485937</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.9380883224177073</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.655635910708617</v>
+        <v>-5.576417325313427</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8483261120916454</v>
+        <v>0.8800135462497214</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.9380883224177073</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.019262155608931</v>
+        <v>-5.94004357021374</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7093631743657616</v>
+        <v>0.741050608523838</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.036309959284833</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.384389538247677</v>
+        <v>-6.305170952852487</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5625667363160942</v>
+        <v>0.5942541704741706</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.332620743583846</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.792978315428355</v>
+        <v>-6.713759730033166</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3978927694585823</v>
+        <v>0.4295802036166578</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.741209520764524</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.205960799569449</v>
+        <v>-7.12674221417426</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2278852082736051</v>
+        <v>0.2595726424316811</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.741209520764524</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.622352673856446</v>
+        <v>-7.543134088461257</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.05932250916768389</v>
+        <v>0.0910099433257594</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.741209520764524</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.999029684386291</v>
+        <v>-7.919811098991102</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08108960437557489</v>
+        <v>-0.04940217021749937</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.741209520764524</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.344904506371099</v>
+        <v>-8.26568592097591</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2233399680238031</v>
+        <v>-0.1916525338657276</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.741209520764524</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.427828191439003</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.2581045219959637</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.724489533249201</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.3729900827908348</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.157838641359437</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5503560305693322</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.540840030102068</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.7036586873879687</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.698238910315188</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.7640467235017869</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-10.05776923281919</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.9025085492053373</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.3841692614842</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-1.025152540714165</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.6033182295584</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.109770377322076</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.59962730460199</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.108294007339511</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.80388547993185</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.184484080352814</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-11.02192325156303</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.267216634520849</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-10.94845341989558</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.222457000360448</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.12357783728213</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.277951546567548</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.35802993129662</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.37895154907494</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.64583377583385</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.500745277663813</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.87565822299768</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.591559266690786</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.10768714273394</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.681677105956176</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-12.05567162876513</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.65688056468225</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.19734347048925</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.71502452827064</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.14775262606441</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.680134780335834</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-11.94860051882731</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.613525071087677</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.7227553661079</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.513607936963705</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.59817670977031</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.462637329872609</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.6510719978146</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.481161670928215</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.52694970005998</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.425779047587732</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.33096092814294</v>
+        <v>-11.41152877592189</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.357120801214782</v>
+        <v>-1.389347940326359</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.052212594487187</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.06712406093887</v>
+        <v>-11.14769190871782</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.261469535646062</v>
+        <v>-1.293696674757638</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.052212594487187</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.79988226007048</v>
+        <v>-10.88045010784942</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.156407375798076</v>
+        <v>-1.188634514909654</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.052212594487187</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.67657633159226</v>
+        <v>-10.7571441793712</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.10738531938025</v>
+        <v>-1.139612458491827</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.962794923359624</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.6526227906163</v>
+        <v>-10.73319063839524</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.097135396844373</v>
+        <v>-1.12936253595595</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.938841382383666</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.3885628522935</v>
+        <v>-10.46913070007244</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.004771737677006</v>
+        <v>-1.036998876788584</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.67478144406087</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.681483228788665</v>
+        <v>-9.762051076567607</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.724726921935372</v>
+        <v>-0.7569540610469492</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.67478144406087</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.641298930422474</v>
+        <v>-9.721866778201417</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7083095787010545</v>
+        <v>-0.7405367178126316</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.634597145694679</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.56122913488467</v>
+        <v>-9.641796982663612</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.676914839265176</v>
+        <v>-0.7091419783767527</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.554527350156875</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.32774791265507</v>
+        <v>-9.408315760434014</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5755979215354836</v>
+        <v>-0.6078250606470617</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.321046127927276</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.148039382511197</v>
+        <v>-9.228607230290141</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5066067197908937</v>
+        <v>-0.5388338589024713</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.26387462376458</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.015763908880309</v>
+        <v>-9.096331756659254</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4583290435915117</v>
+        <v>-0.4905561827030893</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.131599150133694</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.825164234207156</v>
+        <v>-8.9057320819861</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3792741130346133</v>
+        <v>-0.4115012521461914</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.940999475460541</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.576164435523575</v>
+        <v>-8.656732283302519</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2667678523375225</v>
+        <v>-0.2989949914491001</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.940999475460541</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.681754425296679</v>
+        <v>-8.762322273075624</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4369797778459827</v>
+        <v>-0.4692069169575603</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.046589465233645</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.700489327415276</v>
+        <v>-8.781057175194221</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3959293968163351</v>
+        <v>-0.4281565359279131</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.046589465233645</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.552549286007677</v>
+        <v>-8.633117133786621</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.456632302941463</v>
+        <v>-0.488859442053041</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.026268549325088</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.528320649618705</v>
+        <v>-8.608888497397649</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4556548346393523</v>
+        <v>-0.4878819737509299</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.002039912936116</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.484772242848013</v>
+        <v>-8.565340090626957</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4451960840261688</v>
+        <v>-0.4774232231377464</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.002039912936116</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.242623849394155</v>
+        <v>-8.323191697173099</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3338743722634825</v>
+        <v>-0.3661015113750601</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.002039912936116</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.179394477625808</v>
+        <v>-8.259962325404752</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3140505030969485</v>
+        <v>-0.3462776422085261</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.002039912936116</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.056103342808678</v>
+        <v>-8.136671190587622</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2672359551595198</v>
+        <v>-0.2994630942710974</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.878748778118986</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.034954143905235</v>
+        <v>-8.115521991684179</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2510752973608175</v>
+        <v>-0.2833024364723951</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.857599579215542</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.791188701921791</v>
+        <v>-7.871756549700735</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.157788412220389</v>
+        <v>-0.190015551331967</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.857599579215542</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.527160634728531</v>
+        <v>-7.607728482507476</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.05005287142306925</v>
+        <v>-0.08228001053464684</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.655734180399589</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.277310240779457</v>
+        <v>-7.357878088558401</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.04262936114026283</v>
+        <v>0.01040222202868479</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.655734180399589</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.101418148312025</v>
+        <v>-7.181985996090969</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.116585321647884</v>
+        <v>0.08435818253630645</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.655734180399589</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.929971685289561</v>
+        <v>-7.010539533068505</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1984914129114235</v>
+        <v>0.1662642737998454</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.484287717377125</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.704938685620738</v>
+        <v>-6.785506533399682</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2875250903952495</v>
+        <v>0.2552979512836719</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.259254717708302</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.490304307984331</v>
+        <v>-6.570872155763276</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3780736425041296</v>
+        <v>0.345846503392552</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.044620340071896</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.22370395100998</v>
+        <v>-6.304271798788924</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4659080440776657</v>
+        <v>0.4336809049660881</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.044620340071896</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.983273454205119</v>
+        <v>-6.063841301984064</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5638233194244875</v>
+        <v>0.5315961803129094</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8041898432670354</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.740482646555674</v>
+        <v>-5.821050494334618</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6648689563190859</v>
+        <v>0.6326418172075079</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8041898432670354</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.624542796930489</v>
+        <v>-5.705110644709433</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7119234800865</v>
+        <v>0.6796963409749224</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7273681122509115</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.381887208507326</v>
+        <v>-5.46245505628627</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8059837866757587</v>
+        <v>0.7737566475641806</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7273681122509115</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.161866410470315</v>
+        <v>-5.24243425824926</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.895571142901177</v>
+        <v>0.863344003789599</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5861482671829312</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.962617780565506</v>
+        <v>-5.04318562834445</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9911647776649237</v>
+        <v>0.9589376385533459</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5861482671829312</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.803102677046136</v>
+        <v>-4.883670524825081</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.056116663512974</v>
+        <v>1.023889524401396</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4266331636635613</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.658430531946399</v>
+        <v>-4.738998379725343</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.124073624114308</v>
+        <v>1.091846485002731</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2819610185638239</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.718305359304091</v>
+        <v>-4.798873207083036</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.086161184572657</v>
+        <v>1.05393404546108</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.341835845921516</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.631505861525083</v>
+        <v>-4.712073709304027</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.143281477006827</v>
+        <v>1.111054337895249</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.341835845921516</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.633975567986889</v>
+        <v>-4.714543415765833</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.142365995795517</v>
+        <v>1.110138856683939</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3443055523833222</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.702345754310899</v>
+        <v>-4.782913602089844</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.126024843740614</v>
+        <v>1.093797704629037</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3350298533471072</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.580929324684423</v>
+        <v>-4.661497172463367</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.165028124223096</v>
+        <v>1.132800985111519</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3350298533471072</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.611922484013128</v>
+        <v>-4.692490331792072</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9773404255320011</v>
+        <v>0.9451132864204232</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3350298533471072</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.436448224220658</v>
+        <v>-4.517016071999603</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.052097361440777</v>
+        <v>1.019870222329199</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3350298533471072</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.547384476861907</v>
+        <v>-4.627952324640852</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.007734334271075</v>
+        <v>0.9755071951594969</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3350298533471072</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.750411054405141</v>
+        <v>-4.830978902184085</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9296550884736869</v>
+        <v>0.8974279493621091</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.5380564308903406</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.592485455469848</v>
+        <v>-4.673053303248792</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.002997714479936</v>
+        <v>0.9707705753683586</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.5380564308903406</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.740806709280976</v>
+        <v>-4.82137455705992</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9386154835293452</v>
+        <v>0.9063883444177676</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.5380564308903406</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.741989793932037</v>
+        <v>-4.822557641710981</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9299180251134467</v>
+        <v>0.8976908860018689</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.5436994793568521</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.618862086937954</v>
+        <v>-4.699429934716898</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9797209809441814</v>
+        <v>0.9474938418326038</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.5436994793568521</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.526051605487094</v>
+        <v>-4.606619453266038</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9461178654158908</v>
+        <v>0.9138907263043132</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.4508889979059928</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.477488553266064</v>
+        <v>-4.558056401045008</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9674165622289037</v>
+        <v>0.9351894231173259</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4023259456849626</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.364817335029814</v>
+        <v>-4.445385182808758</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.007560758035127</v>
+        <v>0.9753336189235491</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2896547274487124</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.252440333847141</v>
+        <v>-4.333008181626085</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.058002854338863</v>
+        <v>1.025775715227286</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2896547274487124</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.450674902733872</v>
+        <v>-4.531242750512816</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9902062285527098</v>
+        <v>0.9579790894411322</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.487889296335443</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.533676183759151</v>
+        <v>-4.614244031538095</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7953614361432515</v>
+        <v>0.7631342970316739</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5064601808626168</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.374481911702574</v>
+        <v>-4.455049759481518</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9791888056850879</v>
+        <v>0.9469616665735101</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5064601808626168</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660773</v>
+        <v>3.733008865660772</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.369279169221332</v>
+        <v>-4.541648342462621</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9957829287799078</v>
+        <v>0.926835259483392</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5064601808626168</v>
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.739226103081856</v>
+        <v>3.776692144788378</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.838795600967019</v>
+        <v>2.802780311971039</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.369279169221332</v>
+        <v>-4.541648342462621</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9957829287799078</v>
+        <v>0.926835259483392</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.5064601808626168</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.831859397953386</v>
+        <v>2.795844108957407</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240504.xlsx
+++ b/tame_output/ON/bt/strategyON_20240504.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>444.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.7%</t>
+          <t>-599.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.7%</t>
+          <t>-274.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-95.7%</t>
+          <t>-61.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.5%</t>
+          <t>-277.1%</t>
         </is>
       </c>
     </row>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.574254890800635</v>
+        <v>-4.573712406677547</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.307680265929378</v>
+        <v>1.307897259578613</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.8080070932056955</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.006060683950422</v>
+        <v>-5.005518199827335</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.121290836136868</v>
+        <v>1.121507829786103</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.9444245896469625</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.240754678082975</v>
+        <v>-5.240212193959887</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.015698013485937</v>
+        <v>1.015915007135173</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.9380883224177073</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.576417325313427</v>
+        <v>-5.575874841190339</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8800135462497214</v>
+        <v>0.8802305398989567</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.9380883224177073</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.94004357021374</v>
+        <v>-5.939501086090653</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.741050608523838</v>
+        <v>0.7412676021730729</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.036309959284833</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.305170952852487</v>
+        <v>-6.304628468729399</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5942541704741706</v>
+        <v>0.5944711641234055</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.332620743583846</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.713759730033166</v>
+        <v>-6.713217245910078</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4295802036166578</v>
+        <v>0.4297971972658932</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.741209520764524</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.12674221417426</v>
+        <v>-7.126199730051172</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2595726424316811</v>
+        <v>0.259789636080916</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.741209520764524</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.543134088461257</v>
+        <v>-7.54259160433817</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.0910099433257594</v>
+        <v>0.09122693697499429</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.741209520764524</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.919811098991102</v>
+        <v>-7.919268614868014</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04940217021749937</v>
+        <v>-0.04918517656826449</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.741209520764524</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.26568592097591</v>
+        <v>-8.265143436852822</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1916525338657276</v>
+        <v>-0.1914355402164927</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.741209520764524</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.427828191439003</v>
+        <v>-8.427285707315916</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2581045219959637</v>
+        <v>-0.2578875283467288</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.724489533249201</v>
+        <v>-8.723947049126114</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3729900827908348</v>
+        <v>-0.3727730891415999</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.157838641359437</v>
+        <v>-9.157296157236349</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5503560305693322</v>
+        <v>-0.5501390369200969</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.540840030102068</v>
+        <v>-9.54029754597898</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7036586873879687</v>
+        <v>-0.7034416937387338</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.698238910315188</v>
+        <v>-9.697696426192101</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7640467235017869</v>
+        <v>-0.7638297298525516</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.05776923281919</v>
+        <v>-10.0572267486961</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9025085492053373</v>
+        <v>-0.9022915555561024</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.3841692614842</v>
+        <v>-10.38362677736112</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.025152540714165</v>
+        <v>-1.02493554706493</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.6033182295584</v>
+        <v>-10.60277574543531</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.109770377322076</v>
+        <v>-1.10955338367284</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.59962730460199</v>
+        <v>-10.5990848204789</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.108294007339511</v>
+        <v>-1.108077013690276</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.80388547993185</v>
+        <v>-10.80334299580877</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.184484080352814</v>
+        <v>-1.184267086703579</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.02192325156303</v>
+        <v>-11.02138076743994</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.267216634520849</v>
+        <v>-1.266999640871614</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.94845341989558</v>
+        <v>-10.94791093577249</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.222457000360448</v>
+        <v>-1.222240006711213</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.12357783728213</v>
+        <v>-11.12303535315904</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.277951546567548</v>
+        <v>-1.277734552918314</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.35802993129662</v>
+        <v>-11.35748744717353</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.37895154907494</v>
+        <v>-1.378734555425706</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.64583377583385</v>
+        <v>-11.64529129171077</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.500745277663813</v>
+        <v>-1.500528284014577</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.87565822299768</v>
+        <v>-11.87511573887459</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.591559266690786</v>
+        <v>-1.591342273041551</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.10768714273394</v>
+        <v>-12.10714465861085</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.681677105956176</v>
+        <v>-1.681460112306941</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.05567162876513</v>
+        <v>-12.05512914464204</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.65688056468225</v>
+        <v>-1.656663571033015</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.19734347048925</v>
+        <v>-12.19680098636616</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.71502452827064</v>
+        <v>-1.714807534621404</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.14775262606441</v>
+        <v>-12.14721014194133</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.680134780335834</v>
+        <v>-1.679917786686599</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.94860051882731</v>
+        <v>-11.94805803470423</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.613525071087677</v>
+        <v>-1.613308077438442</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.7227553661079</v>
+        <v>-11.72221288198482</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.513607936963705</v>
+        <v>-1.513390943314469</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.59817670977031</v>
+        <v>-11.59763422564722</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.462637329872609</v>
+        <v>-1.462420336223374</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.6510719978146</v>
+        <v>-11.65052951369151</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.481161670928215</v>
+        <v>-1.48094467727898</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.52694970005998</v>
+        <v>-11.36662078276276</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.425779047587732</v>
+        <v>-1.361647480668845</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.41152877592189</v>
+        <v>-11.25119985862467</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.389347940326359</v>
+        <v>-1.325216373407471</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.052212594487187</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14769190871782</v>
+        <v>-10.9873629914206</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.293696674757638</v>
+        <v>-1.229565107838751</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.052212594487187</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.88045010784942</v>
+        <v>-10.7201211905522</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.188634514909654</v>
+        <v>-1.124502947990766</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.052212594487187</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.7571441793712</v>
+        <v>-10.59681526207398</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.139612458491827</v>
+        <v>-1.075480891572939</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.962794923359624</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.73319063839524</v>
+        <v>-10.57286172109802</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.12936253595595</v>
+        <v>-1.065230969037062</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.938841382383666</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.46913070007244</v>
+        <v>-10.30880178277522</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.036998876788584</v>
+        <v>-0.9728673098696952</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.67478144406087</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.762051076567607</v>
+        <v>-9.601722159270388</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7569540610469492</v>
+        <v>-0.6928224941280616</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.67478144406087</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.721866778201417</v>
+        <v>-9.561537860904197</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7405367178126316</v>
+        <v>-0.6764051508937441</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.634597145694679</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.641796982663612</v>
+        <v>-9.481468065366393</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7091419783767527</v>
+        <v>-0.6450104114578652</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.554527350156875</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.408315760434014</v>
+        <v>-9.247986843136793</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6078250606470617</v>
+        <v>-0.5436934937281732</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.321046127927276</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.228607230290141</v>
+        <v>-9.06827831299292</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5388338589024713</v>
+        <v>-0.4747022919835828</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.26387462376458</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.096331756659254</v>
+        <v>-8.936002839362033</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4905561827030893</v>
+        <v>-0.4264246157842009</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.131599150133694</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.9057320819861</v>
+        <v>-8.745403164688879</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4115012521461914</v>
+        <v>-0.3473696852273029</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.940999475460541</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.656732283302519</v>
+        <v>-8.496403366005298</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2989949914491001</v>
+        <v>-0.2348634245302117</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.940999475460541</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.762322273075624</v>
+        <v>-8.601993355778403</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4692069169575603</v>
+        <v>-0.4050753500386719</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.046589465233645</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.781057175194221</v>
+        <v>-8.620728257896999</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4281565359279131</v>
+        <v>-0.3640249690090247</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.046589465233645</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.633117133786621</v>
+        <v>-8.4727882164894</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.488859442053041</v>
+        <v>-0.4247278751341526</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.026268549325088</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.608888497397649</v>
+        <v>-8.448559580100428</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4878819737509299</v>
+        <v>-0.4237504068320415</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.002039912936116</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.565340090626957</v>
+        <v>-8.405011173329736</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4774232231377464</v>
+        <v>-0.413291656218858</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.002039912936116</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.323191697173099</v>
+        <v>-8.162862779875878</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3661015113750601</v>
+        <v>-0.3019699444561716</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.002039912936116</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.259962325404752</v>
+        <v>-8.099633408107531</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3462776422085261</v>
+        <v>-0.2821460752896376</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.002039912936116</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.136671190587622</v>
+        <v>-7.9763422732904</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2994630942710974</v>
+        <v>-0.2353315273522085</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.878748778118986</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.115521991684179</v>
+        <v>-7.955193074386957</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2833024364723951</v>
+        <v>-0.2191708695535062</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.857599579215542</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.871756549700735</v>
+        <v>-7.711427632403512</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.190015551331967</v>
+        <v>-0.1258839844130777</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.857599579215542</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.607728482507476</v>
+        <v>-7.447399565210253</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08228001053464684</v>
+        <v>-0.01814844361575796</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.655734180399589</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.357878088558401</v>
+        <v>-7.197549171261178</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.01040222202868479</v>
+        <v>0.07453378894757412</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.655734180399589</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.181985996090969</v>
+        <v>-7.021657078793746</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08435818253630645</v>
+        <v>0.1484897494551958</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.655734180399589</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.010539533068505</v>
+        <v>-6.850210615771283</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1662642737998454</v>
+        <v>0.2303958407187348</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.484287717377125</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.785506533399682</v>
+        <v>-6.62517761610246</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2552979512836719</v>
+        <v>0.3194295182025608</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.259254717708302</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.570872155763276</v>
+        <v>-6.410543238466053</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.345846503392552</v>
+        <v>0.4099780703114408</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.044620340071896</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.304271798788924</v>
+        <v>-6.143942881491701</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4336809049660881</v>
+        <v>0.4978124718849775</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.044620340071896</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.063841301984064</v>
+        <v>-5.903512384686841</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5315961803129094</v>
+        <v>0.5957277472317988</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8041898432670354</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.821050494334618</v>
+        <v>-5.660721577037395</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6326418172075079</v>
+        <v>0.6967733841263972</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8041898432670354</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.705110644709433</v>
+        <v>-5.54478172741221</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6796963409749224</v>
+        <v>0.7438279078938113</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7273681122509115</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.46245505628627</v>
+        <v>-5.302126138989047</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7737566475641806</v>
+        <v>0.8378882144830699</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7273681122509115</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.24243425824926</v>
+        <v>-5.082105340952037</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.863344003789599</v>
+        <v>0.9274755707084883</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5861482671829312</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.04318562834445</v>
+        <v>-4.882856711047228</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9589376385533459</v>
+        <v>1.023069205472235</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5861482671829312</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.883670524825081</v>
+        <v>-4.723341607527858</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.023889524401396</v>
+        <v>1.088021091320285</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4266331636635613</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.738998379725343</v>
+        <v>-4.57866946242812</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.091846485002731</v>
+        <v>1.15597805192162</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2819610185638239</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.798873207083036</v>
+        <v>-4.638544289785813</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.05393404546108</v>
+        <v>1.118065612379969</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.341835845921516</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.712073709304027</v>
+        <v>-4.551744792006804</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.111054337895249</v>
+        <v>1.175185904814138</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.341835845921516</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.714543415765833</v>
+        <v>-4.55421449846861</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.110138856683939</v>
+        <v>1.174270423602828</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3443055523833222</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.782913602089844</v>
+        <v>-4.622584684792621</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.093797704629037</v>
+        <v>1.157929271547926</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3350298533471072</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978373</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.661497172463367</v>
+        <v>-4.501168255166144</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.132800985111519</v>
+        <v>1.196932552030408</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3350298533471072</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.692490331792072</v>
+        <v>-4.532161414494849</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9451132864204232</v>
+        <v>1.009244853339312</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3350298533471072</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.517016071999603</v>
+        <v>-4.35668715470238</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.019870222329199</v>
+        <v>1.084001789248088</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3350298533471072</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.627952324640852</v>
+        <v>-4.467623407343629</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9755071951594969</v>
+        <v>1.039638762078386</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3350298533471072</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.830978902184085</v>
+        <v>-4.670649984886862</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8974279493621091</v>
+        <v>0.9615595162809982</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.5380564308903406</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.673053303248792</v>
+        <v>-4.512724385951569</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9707705753683586</v>
+        <v>1.034902142287248</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.5380564308903406</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.82137455705992</v>
+        <v>-4.661045639762698</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9063883444177676</v>
+        <v>0.9705199113366567</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.5380564308903406</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.822557641710981</v>
+        <v>-4.662228724413758</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8976908860018689</v>
+        <v>0.961822452920758</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.5436994793568521</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.699429934716898</v>
+        <v>-4.539101017419675</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9474938418326038</v>
+        <v>1.011625408751493</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.5436994793568521</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.606619453266038</v>
+        <v>-4.446290535968815</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9138907263043132</v>
+        <v>0.9780222932232023</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.4508889979059928</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.558056401045008</v>
+        <v>-4.397727483747786</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9351894231173259</v>
+        <v>0.9993209900362152</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4023259456849626</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.445385182808758</v>
+        <v>-4.285056265511535</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9753336189235491</v>
+        <v>1.039465185842438</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2896547274487124</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.333008181626085</v>
+        <v>-4.172679264328862</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.025775715227286</v>
+        <v>1.089907282146175</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2896547274487124</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.531242750512816</v>
+        <v>-4.370913833215593</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9579790894411322</v>
+        <v>1.022110656360021</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.487889296335443</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.614244031538095</v>
+        <v>-4.453915114240872</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7631342970316739</v>
+        <v>0.827265863950563</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5064601808626168</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.455049759481518</v>
+        <v>-4.294720842184296</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9469616665735101</v>
+        <v>1.011093233492399</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5064601808626168</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660772</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.541648342462621</v>
+        <v>-4.381319425165398</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.926835259483392</v>
+        <v>0.9909668264022811</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5064601808626168</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.776692144788378</v>
+        <v>3.776692144788377</v>
       </c>
       <c r="C1954" t="n">
         <v>2.802780311971039</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.541648342462621</v>
+        <v>-4.381319425165398</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.926835259483392</v>
+        <v>0.9909668264022811</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.5064601808626168</v>

--- a/tame_output/ON/bt/strategyON_20240504.xlsx
+++ b/tame_output/ON/bt/strategyON_20240504.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>115.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.8%</t>
+          <t>134.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>-56.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.9%</t>
+          <t>440.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.7%</t>
+          <t>-599.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,52 +1145,52 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-44.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-61.7%</t>
+          <t>-58.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-277.1%</t>
+          <t>-271.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.0%</t>
+          <t>-160.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-274.6%</t>
+          <t>-289.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.4%</t>
+          <t>-205.2%</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.410543238466053</v>
+        <v>-6.561094329495079</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4099780703114408</v>
+        <v>0.3497576338998303</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.044620340071896</v>
+        <v>-1.195171431100922</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.347779585968472</v>
+        <v>2.257448931351057</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.143942881491701</v>
+        <v>-6.294493972520727</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4978124718849775</v>
+        <v>0.4375920354733669</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.044620340071896</v>
+        <v>-1.195171431100922</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.328973844752268</v>
+        <v>2.238643190134852</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.903512384686841</v>
+        <v>-6.054063475715867</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5957277472317988</v>
+        <v>0.5355073108201882</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8041898432670354</v>
+        <v>-0.9547409342960613</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.474975219460061</v>
+        <v>2.384644564842646</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.660721577037395</v>
+        <v>-5.811272668066422</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6967733841263972</v>
+        <v>0.6365529477147867</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8041898432670354</v>
+        <v>-0.9547409342960613</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.478904533294882</v>
+        <v>2.388573878677466</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.54478172741221</v>
+        <v>-5.695332818441236</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7438279078938113</v>
+        <v>0.6836074714822007</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7273681122509115</v>
+        <v>-0.8779192032799374</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.525676155821896</v>
+        <v>2.43534550120448</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.302126138989047</v>
+        <v>-5.452677230018073</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8378882144830699</v>
+        <v>0.7776677780714594</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7273681122509115</v>
+        <v>-0.8779192032799374</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.52267422704189</v>
+        <v>2.432343572424474</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.082105340952037</v>
+        <v>-5.232656431981063</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9274755707084883</v>
+        <v>0.8672551342968777</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5861482671829312</v>
+        <v>-0.7366993582119572</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.608985171093292</v>
+        <v>2.518654516475876</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.882856711047228</v>
+        <v>-5.033407802076254</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.023069205472235</v>
+        <v>0.9628487690606247</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5861482671829312</v>
+        <v>-0.7366993582119572</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.624879353895115</v>
+        <v>2.534548699277699</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.723341607527858</v>
+        <v>-4.873892698556884</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.088021091320285</v>
+        <v>1.027800654908674</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4266331636635613</v>
+        <v>-0.5771842546925873</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.721734260447039</v>
+        <v>2.631403605829624</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.57866946242812</v>
+        <v>-4.729220553457147</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.15597805192162</v>
+        <v>1.095757615510009</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2819610185638239</v>
+        <v>-0.4325121095928499</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.818625650068321</v>
+        <v>2.728294995450906</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.638544289785813</v>
+        <v>-4.789095380814839</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.118065612379969</v>
+        <v>1.057845175968358</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.341835845921516</v>
+        <v>-0.492386936950542</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.768738245055132</v>
+        <v>2.678407590437716</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.551744792006804</v>
+        <v>-4.702295883035831</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.175185904814138</v>
+        <v>1.114965468402528</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.341835845921516</v>
+        <v>-0.492386936950542</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.791138738377698</v>
+        <v>2.700808083760282</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.55421449846861</v>
+        <v>-4.704765589497637</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.174270423602828</v>
+        <v>1.114049987191218</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3443055523833222</v>
+        <v>-0.4948566434123481</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.789729315874026</v>
+        <v>2.699398661256611</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.622584684792621</v>
+        <v>-4.773135775821647</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.157929271547926</v>
+        <v>1.097708835136315</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3350298533471072</v>
+        <v>-0.4855809443761332</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.806301657770457</v>
+        <v>2.715971003153042</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.501168255166144</v>
+        <v>-4.65171934619517</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.196932552030408</v>
+        <v>1.136712115618797</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3350298533471072</v>
+        <v>-0.4855809443761332</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.796738366402348</v>
+        <v>2.706407711784933</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.532161414494849</v>
+        <v>-4.682712505523876</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.009244853339312</v>
+        <v>0.949024416927702</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3350298533471072</v>
+        <v>-0.4855809443761332</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.621447931442735</v>
+        <v>2.53111727682532</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.35668715470238</v>
+        <v>-4.507238245731406</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.084001789248088</v>
+        <v>1.023781352836478</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3350298533471072</v>
+        <v>-0.4855809443761332</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.626015163434523</v>
+        <v>2.535684508817107</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.467623407343629</v>
+        <v>-4.618174498372655</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.039638762078386</v>
+        <v>0.9794183256667757</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3350298533471072</v>
+        <v>-0.4855809443761332</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.626026637321321</v>
+        <v>2.535695982703905</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.670649984886862</v>
+        <v>-4.821201075915888</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9615595162809982</v>
+        <v>0.9013390798693879</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5380564308903406</v>
+        <v>-0.6886075219193666</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.507342076015286</v>
+        <v>2.417011421397871</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.512724385951569</v>
+        <v>-4.663275476980595</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.034902142287248</v>
+        <v>0.9746817058756374</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5380564308903406</v>
+        <v>-0.6886075219193666</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.517514462447418</v>
+        <v>2.427183807830003</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.661045639762698</v>
+        <v>-4.811596730791724</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9705199113366567</v>
+        <v>0.9102994749250461</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5380564308903406</v>
+        <v>-0.6886075219193666</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.512460733021279</v>
+        <v>2.422130078403864</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.662228724413758</v>
+        <v>-4.812779815442784</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.961822452920758</v>
+        <v>0.9016020165091476</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5436994793568521</v>
+        <v>-0.6942505703858781</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.500850679385898</v>
+        <v>2.410520024768482</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.539101017419675</v>
+        <v>-4.689652108448701</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.011625408751493</v>
+        <v>0.9514049723398823</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5436994793568521</v>
+        <v>-0.6942505703858781</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.501402552418999</v>
+        <v>2.411071897801583</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.446290535968815</v>
+        <v>-4.596841626997842</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9780222932232023</v>
+        <v>0.9178018568115918</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4508889979059928</v>
+        <v>-0.6014400889350188</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.48636153318088</v>
+        <v>2.396030878563465</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.397727483747786</v>
+        <v>-4.548278574776812</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9993209900362152</v>
+        <v>0.9391005536246047</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4023259456849626</v>
+        <v>-0.5528770367139886</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.5173728404381</v>
+        <v>2.427042185820684</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.285056265511535</v>
+        <v>-4.435607356540562</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.039465185842438</v>
+        <v>0.9792447494308276</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2896547274487124</v>
+        <v>-0.4402058184777384</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.580051279891572</v>
+        <v>2.489720625274157</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.172679264328862</v>
+        <v>-4.323230355357889</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.089907282146175</v>
+        <v>1.029686845734564</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2896547274487124</v>
+        <v>-0.4402058184777384</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.58554257572224</v>
+        <v>2.495211921104824</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.370913833215593</v>
+        <v>-4.521464924244619</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.022110656360021</v>
+        <v>0.961890219948411</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.487889296335443</v>
+        <v>-0.638440387364469</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.47809903615874</v>
+        <v>2.387768381541325</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.453915114240872</v>
+        <v>-4.604466205269898</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.827265863950563</v>
+        <v>0.7670454275389527</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5064601808626168</v>
+        <v>-0.6570112718916428</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.305312225443089</v>
+        <v>2.214981570825674</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.294720842184296</v>
+        <v>-4.445271933213322</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.011093233492399</v>
+        <v>0.9508727970807889</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5064601808626168</v>
+        <v>-0.6570112718916428</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.425461886162295</v>
+        <v>2.335131231544879</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.381319425165398</v>
+        <v>-4.531870516194425</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9909668264022811</v>
+        <v>0.9307463899906707</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5064601808626168</v>
+        <v>-0.6570112718916428</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.439974912264618</v>
+        <v>2.349644257647202</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.776692144788377</v>
+        <v>3.423377942887989</v>
       </c>
       <c r="C1954" t="n">
         <v>2.802780311971039</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.381319425165398</v>
+        <v>-4.376428074161596</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9909668264022811</v>
+        <v>1.051852657992653</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5064601808626168</v>
+        <v>-0.6570112718916428</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.795844108957407</v>
+        <v>2.408573548836054</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240504.xlsx
+++ b/tame_output/ON/bt/strategyON_20240504.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-37.5%</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.0%</t>
+          <t>114.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.9%</t>
+          <t>133.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-685.6%</t>
+          <t>-675.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.7%</t>
+          <t>-54.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.9%</t>
+          <t>444.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.2%</t>
+          <t>-605.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,62 +1135,62 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.6%</t>
+          <t>-270.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-58.3%</t>
+          <t>-55.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-271.0%</t>
+          <t>-279.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-317.8%</t>
+          <t>-306.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.3%</t>
+          <t>-158.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-289.7%</t>
+          <t>-268.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-191.1%</t>
+          <t>-184.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-205.2%</t>
+          <t>-198.3%</t>
         </is>
       </c>
     </row>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.573712406677547</v>
+        <v>-4.653473476195825</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.307897259578613</v>
+        <v>1.275992831771302</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.8080070932056955</v>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.005518199827335</v>
+        <v>-4.908760686851995</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.121507829786103</v>
+        <v>1.160210834976239</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9444245896469625</v>
+        <v>-0.8304115697268944</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.557416780242606</v>
+        <v>2.625824592194648</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.240212193959887</v>
+        <v>-5.143454680984547</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.015915007135173</v>
+        <v>1.054618012325308</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9380883224177073</v>
+        <v>-0.8240753024976393</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.549503315582251</v>
+        <v>2.617911127534291</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.575874841190339</v>
+        <v>-5.479117328215</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8802305398989567</v>
+        <v>0.9189335450890925</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9380883224177073</v>
+        <v>-0.8240753024976393</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.548083907238215</v>
+        <v>2.616491719190257</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.939501086090653</v>
+        <v>-5.842743573115313</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7412676021730729</v>
+        <v>0.7799706073632087</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.036309959284833</v>
+        <v>-0.9222969393647651</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.495638485352182</v>
+        <v>2.564046297304222</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.304628468729399</v>
+        <v>-6.20787095575406</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5944711641234055</v>
+        <v>0.6331741693135413</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.332620743583846</v>
+        <v>-1.218607723663778</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.317106529778606</v>
+        <v>2.385514341730646</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.713217245910078</v>
+        <v>-6.616459732934738</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4297971972658932</v>
+        <v>0.4685002024560294</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.627196500844456</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.070714807484958</v>
+        <v>2.139122619436998</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.126199730051172</v>
+        <v>-7.029442217075832</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.259789636080916</v>
+        <v>0.2984926412710522</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.627196500844456</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.065900239956418</v>
+        <v>2.134308051908459</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.54259160433817</v>
+        <v>-7.445834091362829</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.09122693697499429</v>
+        <v>0.1299299421651305</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.627196500844456</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.063894290565296</v>
+        <v>2.132302102517336</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.919268614868014</v>
+        <v>-7.822511101892673</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04918517656826449</v>
+        <v>-0.01048217137812824</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.627196500844456</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.074152981233975</v>
+        <v>2.142560793186015</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.265143436852822</v>
+        <v>-8.168385923877482</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1914355402164927</v>
+        <v>-0.1527325350263564</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.627196500844456</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.070252546379669</v>
+        <v>2.138660358331711</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.427285707315916</v>
+        <v>-8.330528194340575</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2578875283467288</v>
+        <v>-0.2191845231565925</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.627196500844456</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.06865746643467</v>
+        <v>2.137065278386712</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.723947049126114</v>
+        <v>-8.627189536150773</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3727730891415999</v>
+        <v>-0.3340700839514636</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.695939636578335</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.031190560923552</v>
+        <v>2.099598372875592</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.157296157236349</v>
+        <v>-9.060538644261008</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5501390369200969</v>
+        <v>-0.5114360317299607</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.695939636578335</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.027164256389149</v>
+        <v>2.095572068341189</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.54029754597898</v>
+        <v>-9.443540033003639</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7034416937387338</v>
+        <v>-0.6647386885485975</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.695939636578335</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.027062155067564</v>
+        <v>2.095469967019605</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.697696426192101</v>
+        <v>-9.60093891321676</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7638297298525516</v>
+        <v>-0.7251267246624153</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.853338516791456</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935194342911122</v>
+        <v>2.003602154863163</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.0572267486961</v>
+        <v>-9.960469235720762</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9022915555561024</v>
+        <v>-0.8635885503659662</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.853338516791456</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.940544646209172</v>
+        <v>2.008952458161213</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.38362677736112</v>
+        <v>-10.28686926438577</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.02493554706493</v>
+        <v>-0.9862325418747937</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.293751565376537</v>
+        <v>-2.179738545456469</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.752620648967342</v>
+        <v>1.821028460919383</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.60277574543531</v>
+        <v>-10.50601823245997</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.10955338367284</v>
+        <v>-1.070850378482703</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.398887513530666</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.624173018744592</v>
+        <v>1.692580830696633</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.5990848204789</v>
+        <v>-10.50232730750356</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.108077013690276</v>
+        <v>-1.06937400850014</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.398887513530666</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.624173018744592</v>
+        <v>1.692580830696633</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.80334299580877</v>
+        <v>-10.70658548283343</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.184267086703579</v>
+        <v>-1.145564081513442</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.640539478064723</v>
+        <v>-2.526526458144655</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.553102849094841</v>
+        <v>1.621510661046882</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.02138076743994</v>
+        <v>-10.9246232544646</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.266999640871614</v>
+        <v>-1.228296635681478</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.815310246160622</v>
+        <v>-2.701297226240554</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.452722942721738</v>
+        <v>1.521130754673779</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.94791093577249</v>
+        <v>-10.85115342279715</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.222240006711213</v>
+        <v>-1.183537001521077</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.741840414493173</v>
+        <v>-2.627827394573106</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.512176543215628</v>
+        <v>1.580584355167669</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.12303535315904</v>
+        <v>-11.0262778401837</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.277734552918314</v>
+        <v>-1.239031547728177</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.802951811959649</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.421657113531219</v>
+        <v>1.490064925483259</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.35748744717353</v>
+        <v>-11.26072993419819</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.378734555425706</v>
+        <v>-1.340031550235569</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.802951811959649</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.414437948629623</v>
+        <v>1.482845760581663</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.64529129171077</v>
+        <v>-11.54853377873543</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.500528284014577</v>
+        <v>-1.461825278824441</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.204768676416955</v>
+        <v>-3.090755656496888</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.235083451133304</v>
+        <v>1.303491263085344</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.87511573887459</v>
+        <v>-11.77835822589925</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.591342273041551</v>
+        <v>-1.552639267851415</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.367416213487116</v>
+        <v>-3.253403193567048</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.138610718729764</v>
+        <v>1.207018530681804</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.10714465861085</v>
+        <v>-12.01038714563551</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.681460112306941</v>
+        <v>-1.642757107116805</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.315415890755471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.104096829045825</v>
+        <v>1.172504640997865</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.05512914464204</v>
+        <v>-11.9583716316667</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.656663571033015</v>
+        <v>-1.617960565842878</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.315415890755471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.108087164732225</v>
+        <v>1.176494976684266</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.19680098636616</v>
+        <v>-12.10004347339082</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.714807534621404</v>
+        <v>-1.676104529431268</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.315415890755471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.106611937833484</v>
+        <v>1.175019749785524</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.14721014194133</v>
+        <v>-12.05045262896599</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.679917786686599</v>
+        <v>-1.641214781496462</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.379838066250705</v>
+        <v>-3.265825046330638</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.151419854653256</v>
+        <v>1.219827666605297</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.94805803470423</v>
+        <v>-11.85130052172889</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.613308077438442</v>
+        <v>-1.574605072248306</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.214515540300892</v>
+        <v>-3.100502520380824</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.237562236576461</v>
+        <v>1.305970048528502</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.72221288198482</v>
+        <v>-11.62545536900948</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.513390943314469</v>
+        <v>-1.474687938124333</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.058575844793661</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.272297314964968</v>
+        <v>1.340705126917009</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.59763422564722</v>
+        <v>-11.50087671267188</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.462420336223374</v>
+        <v>-1.423717331033238</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.058575844793661</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.273436459521027</v>
+        <v>1.341844271473068</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.65052951369151</v>
+        <v>-11.55377200071617</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.48094467727898</v>
+        <v>-1.442241672088844</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.053620498705214</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.279043441336202</v>
+        <v>1.347451253288243</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.36662078276276</v>
+        <v>-11.26986326978742</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.361647480668845</v>
+        <v>-1.322944475478709</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.053620498705214</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.284777145574839</v>
+        <v>1.353184957526879</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.25119985862467</v>
+        <v>-11.20204985073251</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.325216373407471</v>
+        <v>-1.305556370250607</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.052212594487187</v>
+        <v>-2.985807079650297</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.344292437663831</v>
+        <v>1.384135746565964</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.9873629914206</v>
+        <v>-10.93821298352844</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.229565107838751</v>
+        <v>-1.209905104681887</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.052212594487187</v>
+        <v>-2.985807079650297</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.334408956350923</v>
+        <v>1.374252265253057</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.7201211905522</v>
+        <v>-10.67097118266004</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.124502947990766</v>
+        <v>-1.104842944833901</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.052212594487187</v>
+        <v>-2.985807079650297</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.33257439585155</v>
+        <v>1.372417704753683</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.59681526207398</v>
+        <v>-10.54766525418182</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.075480891572939</v>
+        <v>-1.055820888416074</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.962794923359624</v>
+        <v>-2.896389408522734</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.385924683554627</v>
+        <v>1.42576799245676</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.57286172109802</v>
+        <v>-10.52371171320586</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.065230969037062</v>
+        <v>-1.045570965880198</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.938841382383666</v>
+        <v>-2.872435867546777</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.400965314285695</v>
+        <v>1.440808623187828</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.30880178277522</v>
+        <v>-10.25965177488306</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9728673098696952</v>
+        <v>-0.953207306712831</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.67478144406087</v>
+        <v>-2.608375929223981</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.54614096111762</v>
+        <v>1.585984270019754</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.601722159270388</v>
+        <v>-9.552572151378227</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6928224941280616</v>
+        <v>-0.6731624909711971</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.67478144406087</v>
+        <v>-2.608375929223981</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.543353927457319</v>
+        <v>1.583197236359453</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.561537860904197</v>
+        <v>-9.512387853012036</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6764051508937441</v>
+        <v>-0.6567451477368795</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.634597145694679</v>
+        <v>-2.56819163085779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.567808130364875</v>
+        <v>1.607651439267009</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.481468065366393</v>
+        <v>-9.432318057474232</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6450104114578652</v>
+        <v>-0.6253504083010011</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.554527350156875</v>
+        <v>-2.488121835319986</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.615216828908315</v>
+        <v>1.655060137810448</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.247986843136793</v>
+        <v>-9.198836835244634</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5436934937281732</v>
+        <v>-0.5240334905713095</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.321046127927276</v>
+        <v>-2.254640613090387</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.763229991083926</v>
+        <v>1.80307329998606</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.06827831299292</v>
+        <v>-9.019128305100761</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4747022919835828</v>
+        <v>-0.4550422888267192</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.26387462376458</v>
+        <v>-2.197469108927691</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.794640683268585</v>
+        <v>1.834483992170718</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.936002839362033</v>
+        <v>-8.886852831469874</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4264246157842009</v>
+        <v>-0.4067646126273372</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.131599150133694</v>
+        <v>-2.065193635296805</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.869373454194143</v>
+        <v>1.909216763096277</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.745403164688879</v>
+        <v>-8.69625315679672</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3473696852273029</v>
+        <v>-0.3277096820704393</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.940999475460541</v>
+        <v>-1.874593960623652</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.986548319685672</v>
+        <v>2.026391628587805</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.496403366005298</v>
+        <v>-8.447253358113139</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2348634245302117</v>
+        <v>-0.215203421373348</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.940999475460541</v>
+        <v>-1.874593960623652</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.999454660909331</v>
+        <v>2.039297969811464</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.601993355778403</v>
+        <v>-8.552843347886244</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4050753500386719</v>
+        <v>-0.3854153468818087</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.046589465233645</v>
+        <v>-1.980183950396756</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.808124737446249</v>
+        <v>1.847968046348383</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.620728257896999</v>
+        <v>-8.571578250004841</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3640249690090247</v>
+        <v>-0.344364965852161</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.046589465233645</v>
+        <v>-1.980183950396756</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.856669079323336</v>
+        <v>1.896512388225469</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.4727882164894</v>
+        <v>-8.423638208597241</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4247278751341526</v>
+        <v>-0.4050678719772889</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.026268549325088</v>
+        <v>-1.959863034488199</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.748982706180302</v>
+        <v>1.788826015082436</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.448559580100428</v>
+        <v>-8.399409572208269</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4237504068320415</v>
+        <v>-0.4040904036751778</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.002039912936116</v>
+        <v>-1.935634398099226</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.754805901760208</v>
+        <v>1.794649210662341</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.405011173329736</v>
+        <v>-8.355861165437577</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.413291656218858</v>
+        <v>-0.3936316530619948</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.002039912936116</v>
+        <v>-1.935634398099226</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.747845289665114</v>
+        <v>1.787688598567248</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.162862779875878</v>
+        <v>-8.113712771983719</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3019699444561716</v>
+        <v>-0.2823099412993084</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.002039912936116</v>
+        <v>-1.935634398099226</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.762307644046258</v>
+        <v>1.802150952948391</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.099633408107531</v>
+        <v>-8.050483400215372</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2821460752896376</v>
+        <v>-0.2624860721327744</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.002039912936116</v>
+        <v>-1.935634398099226</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.756839764505453</v>
+        <v>1.796683073407586</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.9763422732904</v>
+        <v>-7.927192265398241</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2353315273522085</v>
+        <v>-0.2156715241953449</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.878748778118986</v>
+        <v>-1.812343263282096</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.828312539406308</v>
+        <v>1.868155848308442</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.955193074386957</v>
+        <v>-7.906043066494798</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2191708695535062</v>
+        <v>-0.1995108663966425</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.857599579215542</v>
+        <v>-1.791194064378653</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.848703036985699</v>
+        <v>1.888546345887833</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.711427632403512</v>
+        <v>-7.662277624511353</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1258839844130777</v>
+        <v>-0.106223981256214</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.857599579215542</v>
+        <v>-1.791194064378653</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.84448374533275</v>
+        <v>1.884327054234883</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.447399565210253</v>
+        <v>-7.398249557318094</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.01814844361575796</v>
+        <v>0.001511559541105711</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.655734180399589</v>
+        <v>-1.589328665562699</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.967727298542338</v>
+        <v>2.007570607444471</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.197549171261178</v>
+        <v>-7.148399163369019</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.07453378894757412</v>
+        <v>0.09419379210443779</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.655734180399589</v>
+        <v>-1.589328665562699</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96046937352604</v>
+        <v>2.000312682428174</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.021657078793746</v>
+        <v>-6.972507070901587</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1484897494551958</v>
+        <v>0.1681497526120594</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.655734180399589</v>
+        <v>-1.589328665562699</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.964068497046688</v>
+        <v>2.003911805948822</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.850210615771283</v>
+        <v>-6.801060607879124</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2303958407187348</v>
+        <v>0.2500558438755984</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.484287717377125</v>
+        <v>-1.417882202540236</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.08026388091472</v>
+        <v>2.120107189816854</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.62517761610246</v>
+        <v>-6.576027608210301</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3194295182025608</v>
+        <v>0.3390895213594245</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.259254717708302</v>
+        <v>-1.192849202871413</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.214304158332311</v>
+        <v>2.254147467234445</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.561094329495079</v>
+        <v>-6.361393230573894</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3497576338998303</v>
+        <v>0.4296380734683045</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.195171431100922</v>
+        <v>-0.978214825235006</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.257448931351057</v>
+        <v>2.387622894870606</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.294493972520727</v>
+        <v>-6.094792873599542</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4375920354733669</v>
+        <v>0.5174724750418407</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.195171431100922</v>
+        <v>-0.978214825235006</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.238643190134852</v>
+        <v>2.368817153654402</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.054063475715867</v>
+        <v>-5.854362376794682</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5355073108201882</v>
+        <v>0.6153877503886624</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9547409342960613</v>
+        <v>-0.7377843284301457</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.384644564842646</v>
+        <v>2.514818528362195</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.811272668066422</v>
+        <v>-5.611571569145236</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6365529477147867</v>
+        <v>0.7164333872832609</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9547409342960613</v>
+        <v>-0.7377843284301457</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.388573878677466</v>
+        <v>2.518747842197016</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.695332818441236</v>
+        <v>-5.495631719520051</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6836074714822007</v>
+        <v>0.7634879110506749</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8779192032799374</v>
+        <v>-0.6609625974140219</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.43534550120448</v>
+        <v>2.56551946472403</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.452677230018073</v>
+        <v>-5.252976131096888</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7776677780714594</v>
+        <v>0.8575482176399336</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8779192032799374</v>
+        <v>-0.6609625974140219</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.432343572424474</v>
+        <v>2.562517535944023</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.232656431981063</v>
+        <v>-5.032955333059878</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8672551342968777</v>
+        <v>0.947135573865352</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7366993582119572</v>
+        <v>-0.5197427523460416</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.518654516475876</v>
+        <v>2.648828479995426</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.033407802076254</v>
+        <v>-4.833706703155069</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9628487690606247</v>
+        <v>1.042729208629099</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7366993582119572</v>
+        <v>-0.5197427523460416</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.534548699277699</v>
+        <v>2.664722662797249</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.873892698556884</v>
+        <v>-4.674191599635699</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.027800654908674</v>
+        <v>1.107681094477149</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5771842546925873</v>
+        <v>-0.3602276488266717</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.631403605829624</v>
+        <v>2.761577569349173</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.729220553457147</v>
+        <v>-4.529519454535961</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.095757615510009</v>
+        <v>1.175638055078484</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4325121095928499</v>
+        <v>-0.2155555037269343</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.728294995450906</v>
+        <v>2.858468958970455</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.789095380814839</v>
+        <v>-4.589394281893654</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.057845175968358</v>
+        <v>1.137725615536832</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.492386936950542</v>
+        <v>-0.2754303310846264</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.678407590437716</v>
+        <v>2.808581553957266</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.702295883035831</v>
+        <v>-4.502594784114645</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.114965468402528</v>
+        <v>1.194845907971002</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.492386936950542</v>
+        <v>-0.2754303310846264</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.700808083760282</v>
+        <v>2.830982047279832</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.704765589497637</v>
+        <v>-4.505064490576451</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.114049987191218</v>
+        <v>1.193930426759692</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4948566434123481</v>
+        <v>-0.2779000375464326</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.699398661256611</v>
+        <v>2.82957262477616</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.773135775821647</v>
+        <v>-4.573434676900462</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.097708835136315</v>
+        <v>1.177589274704789</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4855809443761332</v>
+        <v>-0.2686243385102176</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.715971003153042</v>
+        <v>2.846144966672591</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.65171934619517</v>
+        <v>-4.452018247273985</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.136712115618797</v>
+        <v>1.216592555187271</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4855809443761332</v>
+        <v>-0.2686243385102176</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.706407711784933</v>
+        <v>2.836581675304482</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.682712505523876</v>
+        <v>-4.48301140660269</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.949024416927702</v>
+        <v>1.028904856496176</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4855809443761332</v>
+        <v>-0.2686243385102176</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.53111727682532</v>
+        <v>2.661291240344869</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.507238245731406</v>
+        <v>-4.307537146810221</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.023781352836478</v>
+        <v>1.103661792404952</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4855809443761332</v>
+        <v>-0.2686243385102176</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.535684508817107</v>
+        <v>2.665858472336657</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.618174498372655</v>
+        <v>-4.41847339945147</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9794183256667757</v>
+        <v>1.05929876523525</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4855809443761332</v>
+        <v>-0.2686243385102176</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.535695982703905</v>
+        <v>2.665869946223455</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.821201075915888</v>
+        <v>-4.621499976994703</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9013390798693879</v>
+        <v>0.9812195194378619</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6886075219193666</v>
+        <v>-0.471650916053451</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.417011421397871</v>
+        <v>2.54718538491742</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.663275476980595</v>
+        <v>-4.46357437805941</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9746817058756374</v>
+        <v>1.054562145444111</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6886075219193666</v>
+        <v>-0.471650916053451</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.427183807830003</v>
+        <v>2.557357771349552</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.811596730791724</v>
+        <v>-4.611895631870539</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9102994749250461</v>
+        <v>0.9901799144935204</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6886075219193666</v>
+        <v>-0.471650916053451</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.422130078403864</v>
+        <v>2.552304041923413</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.812779815442784</v>
+        <v>-4.613078716521599</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9016020165091476</v>
+        <v>0.9814824560776216</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6942505703858781</v>
+        <v>-0.4772939645199625</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.410520024768482</v>
+        <v>2.540693988288032</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.689652108448701</v>
+        <v>-4.489951009527516</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9514049723398823</v>
+        <v>1.031285411908356</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6942505703858781</v>
+        <v>-0.4772939645199625</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.411071897801583</v>
+        <v>2.541245861321133</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.596841626997842</v>
+        <v>-4.397140528076656</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9178018568115918</v>
+        <v>0.997682296380066</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6014400889350188</v>
+        <v>-0.3844834830691032</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.396030878563465</v>
+        <v>2.526204842083014</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.548278574776812</v>
+        <v>-4.348577475855627</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9391005536246047</v>
+        <v>1.018980993193079</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5528770367139886</v>
+        <v>-0.335920430848073</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.427042185820684</v>
+        <v>2.557216149340233</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.435607356540562</v>
+        <v>-4.235906257619376</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9792447494308276</v>
+        <v>1.059125188999302</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4402058184777384</v>
+        <v>-0.2232492126118228</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.489720625274157</v>
+        <v>2.619894588793706</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.323230355357889</v>
+        <v>-4.123529256436703</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.029686845734564</v>
+        <v>1.109567285303038</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4402058184777384</v>
+        <v>-0.2232492126118228</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.495211921104824</v>
+        <v>2.625385884624373</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.521464924244619</v>
+        <v>-4.321763825323434</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.961890219948411</v>
+        <v>1.041770659516885</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.638440387364469</v>
+        <v>-0.4214837814985534</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.387768381541325</v>
+        <v>2.517942345060874</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.604466205269898</v>
+        <v>-4.404765106348713</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7670454275389527</v>
+        <v>0.8469258671074267</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6570112718916428</v>
+        <v>-0.4400546660257271</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.214981570825674</v>
+        <v>2.345155534345223</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.445271933213322</v>
+        <v>-4.245570834292137</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9508727970807889</v>
+        <v>1.030753236649263</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6570112718916428</v>
+        <v>-0.4400546660257271</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.335131231544879</v>
+        <v>2.465305195064429</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.531870516194425</v>
+        <v>-4.332169417273239</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9307463899906707</v>
+        <v>1.010626829559145</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6570112718916428</v>
+        <v>-0.4400546660257271</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.349644257647202</v>
+        <v>2.479818221166752</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.423377942887989</v>
+        <v>3.709945604389168</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.802780311971039</v>
+        <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.376428074161596</v>
+        <v>-4.436818271544198</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.051852657992653</v>
+        <v>0.9661867291931303</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.6570112718916428</v>
+        <v>-0.4400546660257271</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.408573548836054</v>
+        <v>2.477237662509121</v>
       </c>
     </row>
   </sheetData>
